--- a/informes_data/Tercera FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_C.B. CUARTE DE HUERVA.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_C.B. CUARTE DE HUERVA.xlsx
@@ -565,13 +565,13 @@
         <v>4</v>
       </c>
       <c r="D2" t="n">
-        <v>19.9833</v>
+        <v>22.0203</v>
       </c>
       <c r="E2" t="n">
-        <v>18.0997</v>
+        <v>18.8879</v>
       </c>
       <c r="F2" t="n">
-        <v>1.8836</v>
+        <v>3.1325</v>
       </c>
       <c r="G2" t="n">
         <v>17.6194</v>
@@ -610,13 +610,13 @@
         <v>8.399800000000001</v>
       </c>
       <c r="S2" t="n">
-        <v>-3.2506</v>
+        <v>-1.2135</v>
       </c>
       <c r="T2" t="n">
-        <v>-2.5881</v>
+        <v>-1.8001</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.6621</v>
+        <v>0.5865999999999999</v>
       </c>
       <c r="V2" t="n">
         <v>9.1305</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A. YOUNG MEDIERO</t>
+          <t>S. MENENDEZ PEREZ</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -640,76 +640,76 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="D3" t="n">
-        <v>13.2639</v>
+        <v>18.4149</v>
       </c>
       <c r="E3" t="n">
-        <v>8.3215</v>
+        <v>24.7425</v>
       </c>
       <c r="F3" t="n">
-        <v>4.942699999999999</v>
+        <v>-6.327299999999998</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.9678999999999993</v>
+        <v>6.1248</v>
       </c>
       <c r="H3" t="n">
-        <v>7.2208</v>
+        <v>5.5973</v>
       </c>
       <c r="I3" t="n">
-        <v>-8.188600000000001</v>
+        <v>0.527399999999999</v>
       </c>
       <c r="J3" t="n">
-        <v>11.579</v>
+        <v>53.4568</v>
       </c>
       <c r="K3" t="n">
-        <v>13.1505</v>
+        <v>32.539</v>
       </c>
       <c r="L3" t="n">
-        <v>-1.5713</v>
+        <v>20.9181</v>
       </c>
       <c r="M3" t="n">
-        <v>-12.5469</v>
+        <v>-47.3318</v>
       </c>
       <c r="N3" t="n">
-        <v>-5.929600000000001</v>
+        <v>-26.9419</v>
       </c>
       <c r="O3" t="n">
-        <v>-6.6173</v>
+        <v>-20.3902</v>
       </c>
       <c r="P3" t="n">
-        <v>5.8604</v>
+        <v>10.7438</v>
       </c>
       <c r="Q3" t="n">
-        <v>-10.7438</v>
+        <v>-33.9894</v>
       </c>
       <c r="R3" t="n">
-        <v>16.6043</v>
+        <v>44.7336</v>
       </c>
       <c r="S3" t="n">
-        <v>9.236799999999999</v>
+        <v>-1.9876</v>
       </c>
       <c r="T3" t="n">
-        <v>2.2219</v>
+        <v>-8.799799999999999</v>
       </c>
       <c r="U3" t="n">
-        <v>7.0149</v>
+        <v>6.8123</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.8651</v>
+        <v>3.5338</v>
       </c>
       <c r="W3" t="n">
-        <v>5.2643</v>
+        <v>14.0748</v>
       </c>
       <c r="X3" t="n">
-        <v>-6.1297</v>
+        <v>-10.5409</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>S. MENENDEZ PEREZ</t>
+          <t>P. GIMENO MARTIN</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -718,76 +718,76 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D4" t="n">
-        <v>10.7288</v>
+        <v>15.9676</v>
       </c>
       <c r="E4" t="n">
-        <v>18.8589</v>
+        <v>28.1123</v>
       </c>
       <c r="F4" t="n">
-        <v>-8.129899999999999</v>
+        <v>-12.1444</v>
       </c>
       <c r="G4" t="n">
-        <v>6.1248</v>
+        <v>15.4114</v>
       </c>
       <c r="H4" t="n">
-        <v>5.5973</v>
+        <v>30.8557</v>
       </c>
       <c r="I4" t="n">
-        <v>0.527399999999999</v>
+        <v>-15.4445</v>
       </c>
       <c r="J4" t="n">
-        <v>53.4568</v>
+        <v>62.7335</v>
       </c>
       <c r="K4" t="n">
-        <v>32.539</v>
+        <v>56.4375</v>
       </c>
       <c r="L4" t="n">
-        <v>20.9181</v>
+        <v>6.2959</v>
       </c>
       <c r="M4" t="n">
-        <v>-47.3318</v>
+        <v>-47.322</v>
       </c>
       <c r="N4" t="n">
-        <v>-26.9419</v>
+        <v>-25.582</v>
       </c>
       <c r="O4" t="n">
-        <v>-20.3902</v>
+        <v>-21.7399</v>
       </c>
       <c r="P4" t="n">
-        <v>10.7438</v>
+        <v>-7.0323</v>
       </c>
       <c r="Q4" t="n">
-        <v>-33.9894</v>
+        <v>-53.3284</v>
       </c>
       <c r="R4" t="n">
-        <v>44.7336</v>
+        <v>46.2963</v>
       </c>
       <c r="S4" t="n">
-        <v>-9.674199999999999</v>
+        <v>-3.8264</v>
       </c>
       <c r="T4" t="n">
-        <v>-14.6831</v>
+        <v>-9.664899999999999</v>
       </c>
       <c r="U4" t="n">
-        <v>5.0092</v>
+        <v>5.8384</v>
       </c>
       <c r="V4" t="n">
-        <v>3.5338</v>
+        <v>11.4153</v>
       </c>
       <c r="W4" t="n">
-        <v>14.0748</v>
+        <v>28.3726</v>
       </c>
       <c r="X4" t="n">
-        <v>-10.5409</v>
+        <v>-16.9569</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>M. PORTALEZ MUR</t>
+          <t>A. YOUNG MEDIERO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -796,76 +796,76 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="D5" t="n">
-        <v>9.785900000000002</v>
+        <v>9.584500000000002</v>
       </c>
       <c r="E5" t="n">
-        <v>1.7622</v>
+        <v>6.176600000000001</v>
       </c>
       <c r="F5" t="n">
-        <v>8.023700000000002</v>
+        <v>3.4078</v>
       </c>
       <c r="G5" t="n">
-        <v>7.055400000000001</v>
+        <v>-0.9678999999999993</v>
       </c>
       <c r="H5" t="n">
-        <v>31.5738</v>
+        <v>7.2208</v>
       </c>
       <c r="I5" t="n">
-        <v>-24.5184</v>
+        <v>-8.188600000000001</v>
       </c>
       <c r="J5" t="n">
-        <v>46.2183</v>
+        <v>11.579</v>
       </c>
       <c r="K5" t="n">
-        <v>52.2358</v>
+        <v>13.1505</v>
       </c>
       <c r="L5" t="n">
-        <v>-6.0177</v>
+        <v>-1.5713</v>
       </c>
       <c r="M5" t="n">
-        <v>-39.1625</v>
+        <v>-12.5469</v>
       </c>
       <c r="N5" t="n">
-        <v>-20.662</v>
+        <v>-5.929600000000001</v>
       </c>
       <c r="O5" t="n">
-        <v>-18.5006</v>
+        <v>-6.6173</v>
       </c>
       <c r="P5" t="n">
-        <v>-18.7529</v>
+        <v>5.8604</v>
       </c>
       <c r="Q5" t="n">
-        <v>-57.4306</v>
+        <v>-10.7438</v>
       </c>
       <c r="R5" t="n">
-        <v>38.6779</v>
+        <v>16.6043</v>
       </c>
       <c r="S5" t="n">
-        <v>16.6822</v>
+        <v>5.557399999999999</v>
       </c>
       <c r="T5" t="n">
-        <v>-2.4864</v>
+        <v>0.07709999999999999</v>
       </c>
       <c r="U5" t="n">
-        <v>19.1684</v>
+        <v>5.4801</v>
       </c>
       <c r="V5" t="n">
-        <v>4.8013</v>
+        <v>-0.8651</v>
       </c>
       <c r="W5" t="n">
-        <v>15.4613</v>
+        <v>5.2643</v>
       </c>
       <c r="X5" t="n">
-        <v>-10.6598</v>
+        <v>-6.1297</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>P. GIMENO MARTIN</t>
+          <t>F. ALEN GARCIA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -874,76 +874,76 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="D6" t="n">
-        <v>4.629199999999999</v>
+        <v>2.4485</v>
       </c>
       <c r="E6" t="n">
-        <v>23.7055</v>
+        <v>1.7746</v>
       </c>
       <c r="F6" t="n">
-        <v>-19.0759</v>
+        <v>0.6739999999999999</v>
       </c>
       <c r="G6" t="n">
-        <v>15.4114</v>
+        <v>0.9076000000000002</v>
       </c>
       <c r="H6" t="n">
-        <v>30.8557</v>
+        <v>0.4768000000000002</v>
       </c>
       <c r="I6" t="n">
-        <v>-15.4445</v>
+        <v>0.4307</v>
       </c>
       <c r="J6" t="n">
-        <v>62.7335</v>
+        <v>1.0674</v>
       </c>
       <c r="K6" t="n">
-        <v>56.4375</v>
+        <v>0.9055</v>
       </c>
       <c r="L6" t="n">
-        <v>6.2959</v>
+        <v>0.1619</v>
       </c>
       <c r="M6" t="n">
-        <v>-47.322</v>
+        <v>-0.1599</v>
       </c>
       <c r="N6" t="n">
-        <v>-25.582</v>
+        <v>-0.4288</v>
       </c>
       <c r="O6" t="n">
-        <v>-21.7399</v>
+        <v>0.2688</v>
       </c>
       <c r="P6" t="n">
-        <v>-7.0323</v>
+        <v>0.9766999999999999</v>
       </c>
       <c r="Q6" t="n">
-        <v>-53.3284</v>
+        <v>-0.1953</v>
       </c>
       <c r="R6" t="n">
-        <v>46.2963</v>
+        <v>1.172</v>
       </c>
       <c r="S6" t="n">
-        <v>-15.165</v>
+        <v>-0.432</v>
       </c>
       <c r="T6" t="n">
-        <v>-14.072</v>
+        <v>-0.2613</v>
       </c>
       <c r="U6" t="n">
-        <v>-1.093</v>
+        <v>-0.1707</v>
       </c>
       <c r="V6" t="n">
-        <v>11.4153</v>
+        <v>0.9963</v>
       </c>
       <c r="W6" t="n">
-        <v>28.3726</v>
+        <v>1.1637</v>
       </c>
       <c r="X6" t="n">
-        <v>-16.9569</v>
+        <v>-0.1676</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>F. ALEN GARCIA</t>
+          <t>M. PORTALEZ MUR</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -952,70 +952,70 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="D7" t="n">
-        <v>2.4139</v>
+        <v>0.5248999999999997</v>
       </c>
       <c r="E7" t="n">
-        <v>2.1185</v>
+        <v>-1.4347</v>
       </c>
       <c r="F7" t="n">
-        <v>0.2953000000000001</v>
+        <v>1.9598</v>
       </c>
       <c r="G7" t="n">
-        <v>0.9076000000000002</v>
+        <v>7.055400000000001</v>
       </c>
       <c r="H7" t="n">
-        <v>0.4768000000000002</v>
+        <v>31.5738</v>
       </c>
       <c r="I7" t="n">
-        <v>0.4307</v>
+        <v>-24.5184</v>
       </c>
       <c r="J7" t="n">
-        <v>1.0674</v>
+        <v>46.2183</v>
       </c>
       <c r="K7" t="n">
-        <v>0.9055</v>
+        <v>52.2358</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1619</v>
+        <v>-6.0177</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.1599</v>
+        <v>-39.1625</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.4288</v>
+        <v>-20.662</v>
       </c>
       <c r="O7" t="n">
-        <v>0.2688</v>
+        <v>-18.5006</v>
       </c>
       <c r="P7" t="n">
-        <v>0.9766999999999999</v>
+        <v>-18.7529</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.1953</v>
+        <v>-57.4306</v>
       </c>
       <c r="R7" t="n">
-        <v>1.172</v>
+        <v>38.6779</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.4667</v>
+        <v>7.421</v>
       </c>
       <c r="T7" t="n">
-        <v>0.0827</v>
+        <v>-5.6834</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.5493</v>
+        <v>13.1045</v>
       </c>
       <c r="V7" t="n">
-        <v>0.9963</v>
+        <v>4.8013</v>
       </c>
       <c r="W7" t="n">
-        <v>1.1637</v>
+        <v>15.4613</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.1676</v>
+        <v>-10.6598</v>
       </c>
     </row>
     <row r="8">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.5467</v>
+        <v>-2.356</v>
       </c>
       <c r="E11" t="n">
         <v>-1.8128</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.7338</v>
+        <v>-0.5432</v>
       </c>
       <c r="G11" t="n">
         <v>-1.7851</v>
@@ -1312,13 +1312,13 @@
         <v>0.586</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.1755</v>
+        <v>0.0151</v>
       </c>
       <c r="T11" t="n">
         <v>0.311</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.4865</v>
+        <v>-0.2958</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1345,13 +1345,13 @@
         <v>8</v>
       </c>
       <c r="D12" t="n">
-        <v>-6.5528</v>
+        <v>-5.758699999999999</v>
       </c>
       <c r="E12" t="n">
-        <v>-8.284099999999999</v>
+        <v>-7.779900000000001</v>
       </c>
       <c r="F12" t="n">
-        <v>1.7313</v>
+        <v>2.021199999999999</v>
       </c>
       <c r="G12" t="n">
         <v>7.019</v>
@@ -1390,13 +1390,13 @@
         <v>13.4788</v>
       </c>
       <c r="S12" t="n">
-        <v>2.2656</v>
+        <v>3.06</v>
       </c>
       <c r="T12" t="n">
-        <v>-2.2411</v>
+        <v>-1.7369</v>
       </c>
       <c r="U12" t="n">
-        <v>4.5067</v>
+        <v>4.7969</v>
       </c>
       <c r="V12" t="n">
         <v>-1.9683</v>
@@ -1411,7 +1411,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>T. SEKOU MOUSSA</t>
+          <t>M. KOTSEV</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1420,76 +1420,76 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="D13" t="n">
-        <v>-8.194800000000001</v>
+        <v>-9.2121</v>
       </c>
       <c r="E13" t="n">
-        <v>-6.9434</v>
+        <v>-3.431100000000001</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.2514</v>
+        <v>-5.781199999999999</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.8016000000000003</v>
+        <v>-4.1777</v>
       </c>
       <c r="H13" t="n">
-        <v>-1.5276</v>
+        <v>-7.815399999999999</v>
       </c>
       <c r="I13" t="n">
-        <v>0.7261000000000001</v>
+        <v>3.6375</v>
       </c>
       <c r="J13" t="n">
-        <v>0.6217</v>
+        <v>14.1097</v>
       </c>
       <c r="K13" t="n">
-        <v>0.2980000000000002</v>
+        <v>3.856200000000001</v>
       </c>
       <c r="L13" t="n">
-        <v>0.3237</v>
+        <v>10.2538</v>
       </c>
       <c r="M13" t="n">
-        <v>-1.4233</v>
+        <v>-18.2873</v>
       </c>
       <c r="N13" t="n">
-        <v>-1.8255</v>
+        <v>-11.6715</v>
       </c>
       <c r="O13" t="n">
-        <v>0.4022</v>
+        <v>-6.616</v>
       </c>
       <c r="P13" t="n">
-        <v>-6.6417</v>
+        <v>-6.4464</v>
       </c>
       <c r="Q13" t="n">
-        <v>-9.9625</v>
+        <v>-23.0504</v>
       </c>
       <c r="R13" t="n">
-        <v>3.3208</v>
+        <v>16.6041</v>
       </c>
       <c r="S13" t="n">
-        <v>3.8578</v>
+        <v>-1.0467</v>
       </c>
       <c r="T13" t="n">
-        <v>3.7257</v>
+        <v>-1.3056</v>
       </c>
       <c r="U13" t="n">
-        <v>0.1321</v>
+        <v>0.2587999999999999</v>
       </c>
       <c r="V13" t="n">
-        <v>-4.609500000000001</v>
+        <v>2.458699999999999</v>
       </c>
       <c r="W13" t="n">
-        <v>-1.3284</v>
+        <v>6.8151</v>
       </c>
       <c r="X13" t="n">
-        <v>-3.2811</v>
+        <v>-4.3565</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>M. KOTSEV</t>
+          <t>T. SEKOU MOUSSA</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1498,76 +1498,76 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="D14" t="n">
-        <v>-10.176</v>
+        <v>-11.5177</v>
       </c>
       <c r="E14" t="n">
-        <v>-3.3898</v>
+        <v>-9.774699999999999</v>
       </c>
       <c r="F14" t="n">
-        <v>-6.786</v>
+        <v>-1.7429</v>
       </c>
       <c r="G14" t="n">
-        <v>-4.1777</v>
+        <v>-0.8016000000000003</v>
       </c>
       <c r="H14" t="n">
-        <v>-7.815399999999999</v>
+        <v>-1.5276</v>
       </c>
       <c r="I14" t="n">
-        <v>3.6375</v>
+        <v>0.7261000000000001</v>
       </c>
       <c r="J14" t="n">
-        <v>14.1097</v>
+        <v>0.6217</v>
       </c>
       <c r="K14" t="n">
-        <v>3.856200000000001</v>
+        <v>0.2980000000000002</v>
       </c>
       <c r="L14" t="n">
-        <v>10.2538</v>
+        <v>0.3237</v>
       </c>
       <c r="M14" t="n">
-        <v>-18.2873</v>
+        <v>-1.4233</v>
       </c>
       <c r="N14" t="n">
-        <v>-11.6715</v>
+        <v>-1.8255</v>
       </c>
       <c r="O14" t="n">
-        <v>-6.616</v>
+        <v>0.4022</v>
       </c>
       <c r="P14" t="n">
-        <v>-6.4464</v>
+        <v>-6.6417</v>
       </c>
       <c r="Q14" t="n">
-        <v>-23.0504</v>
+        <v>-9.9625</v>
       </c>
       <c r="R14" t="n">
-        <v>16.6041</v>
+        <v>3.3208</v>
       </c>
       <c r="S14" t="n">
-        <v>-2.0105</v>
+        <v>0.5349999999999999</v>
       </c>
       <c r="T14" t="n">
-        <v>-1.2644</v>
+        <v>0.8945</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.7461000000000001</v>
+        <v>-0.3596</v>
       </c>
       <c r="V14" t="n">
-        <v>2.458699999999999</v>
+        <v>-4.609500000000001</v>
       </c>
       <c r="W14" t="n">
-        <v>6.8151</v>
+        <v>-1.3284</v>
       </c>
       <c r="X14" t="n">
-        <v>-4.3565</v>
+        <v>-3.2811</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>F. GASPAR AGUILAR</t>
+          <t>J. FERNANDEZ MANZANARES</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1576,76 +1576,76 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="D15" t="n">
-        <v>-12.4071</v>
+        <v>-13.5641</v>
       </c>
       <c r="E15" t="n">
-        <v>-7.1361</v>
+        <v>1.405199999999999</v>
       </c>
       <c r="F15" t="n">
-        <v>-5.2708</v>
+        <v>-14.9691</v>
       </c>
       <c r="G15" t="n">
-        <v>-6.8886</v>
+        <v>-30.3707</v>
       </c>
       <c r="H15" t="n">
-        <v>-5.387</v>
+        <v>-12.3136</v>
       </c>
       <c r="I15" t="n">
-        <v>-1.5017</v>
+        <v>-18.057</v>
       </c>
       <c r="J15" t="n">
-        <v>2.1217</v>
+        <v>26.7924</v>
       </c>
       <c r="K15" t="n">
-        <v>0.2454</v>
+        <v>23.106</v>
       </c>
       <c r="L15" t="n">
-        <v>1.8762</v>
+        <v>3.686399999999999</v>
       </c>
       <c r="M15" t="n">
-        <v>-9.010199999999999</v>
+        <v>-57.1636</v>
       </c>
       <c r="N15" t="n">
-        <v>-5.6325</v>
+        <v>-35.4199</v>
       </c>
       <c r="O15" t="n">
-        <v>-3.3777</v>
+        <v>-21.7437</v>
       </c>
       <c r="P15" t="n">
-        <v>-1.5626</v>
+        <v>2.7349</v>
       </c>
       <c r="Q15" t="n">
-        <v>-13.6739</v>
+        <v>-46.4916</v>
       </c>
       <c r="R15" t="n">
-        <v>12.1114</v>
+        <v>49.2263</v>
       </c>
       <c r="S15" t="n">
-        <v>5.0289</v>
+        <v>2.9336</v>
       </c>
       <c r="T15" t="n">
-        <v>4.0263</v>
+        <v>-7.7679</v>
       </c>
       <c r="U15" t="n">
-        <v>1.0026</v>
+        <v>10.702</v>
       </c>
       <c r="V15" t="n">
-        <v>-8.984400000000001</v>
+        <v>11.138</v>
       </c>
       <c r="W15" t="n">
-        <v>0.3898</v>
+        <v>28.8719</v>
       </c>
       <c r="X15" t="n">
-        <v>-9.3741</v>
+        <v>-17.7338</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>J. FERNANDEZ MANZANARES</t>
+          <t>M. PACÍFICO CANTARELLI</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1654,76 +1654,76 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="D16" t="n">
-        <v>-14.8093</v>
+        <v>-16.1221</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.270399999999999</v>
+        <v>-7.8285</v>
       </c>
       <c r="F16" t="n">
-        <v>-14.5387</v>
+        <v>-8.293900000000001</v>
       </c>
       <c r="G16" t="n">
-        <v>-30.3707</v>
+        <v>-9.3651</v>
       </c>
       <c r="H16" t="n">
-        <v>-12.3136</v>
+        <v>-6.261699999999999</v>
       </c>
       <c r="I16" t="n">
-        <v>-18.057</v>
+        <v>-3.1037</v>
       </c>
       <c r="J16" t="n">
-        <v>26.7924</v>
+        <v>3.9957</v>
       </c>
       <c r="K16" t="n">
-        <v>23.106</v>
+        <v>0.7531999999999998</v>
       </c>
       <c r="L16" t="n">
-        <v>3.686399999999999</v>
+        <v>3.242099999999999</v>
       </c>
       <c r="M16" t="n">
-        <v>-57.1636</v>
+        <v>-13.3605</v>
       </c>
       <c r="N16" t="n">
-        <v>-35.4199</v>
+        <v>-7.014799999999999</v>
       </c>
       <c r="O16" t="n">
-        <v>-21.7437</v>
+        <v>-6.3458</v>
       </c>
       <c r="P16" t="n">
-        <v>2.7349</v>
+        <v>-3.5161</v>
       </c>
       <c r="Q16" t="n">
-        <v>-46.4916</v>
+        <v>-14.2599</v>
       </c>
       <c r="R16" t="n">
-        <v>49.2263</v>
+        <v>10.7437</v>
       </c>
       <c r="S16" t="n">
-        <v>1.6885</v>
+        <v>-1.8001</v>
       </c>
       <c r="T16" t="n">
-        <v>-9.4436</v>
+        <v>-2.3288</v>
       </c>
       <c r="U16" t="n">
-        <v>11.132</v>
+        <v>0.5289</v>
       </c>
       <c r="V16" t="n">
-        <v>11.138</v>
+        <v>-1.4412</v>
       </c>
       <c r="W16" t="n">
-        <v>28.8719</v>
+        <v>4.764699999999999</v>
       </c>
       <c r="X16" t="n">
-        <v>-17.7338</v>
+        <v>-6.2058</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>M. PACÍFICO CANTARELLI</t>
+          <t>F. GASPAR AGUILAR</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1732,70 +1732,70 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="D17" t="n">
-        <v>-19.861</v>
+        <v>-16.9687</v>
       </c>
       <c r="E17" t="n">
-        <v>-8.495100000000001</v>
+        <v>-10.9585</v>
       </c>
       <c r="F17" t="n">
-        <v>-11.3659</v>
+        <v>-6.010199999999999</v>
       </c>
       <c r="G17" t="n">
-        <v>-9.3651</v>
+        <v>-6.8886</v>
       </c>
       <c r="H17" t="n">
-        <v>-6.261699999999999</v>
+        <v>-5.387</v>
       </c>
       <c r="I17" t="n">
-        <v>-3.1037</v>
+        <v>-1.5017</v>
       </c>
       <c r="J17" t="n">
-        <v>3.9957</v>
+        <v>2.1217</v>
       </c>
       <c r="K17" t="n">
-        <v>0.7531999999999998</v>
+        <v>0.2454</v>
       </c>
       <c r="L17" t="n">
-        <v>3.242099999999999</v>
+        <v>1.8762</v>
       </c>
       <c r="M17" t="n">
-        <v>-13.3605</v>
+        <v>-9.010199999999999</v>
       </c>
       <c r="N17" t="n">
-        <v>-7.014799999999999</v>
+        <v>-5.6325</v>
       </c>
       <c r="O17" t="n">
-        <v>-6.3458</v>
+        <v>-3.3777</v>
       </c>
       <c r="P17" t="n">
-        <v>-3.5161</v>
+        <v>-1.5626</v>
       </c>
       <c r="Q17" t="n">
-        <v>-14.2599</v>
+        <v>-13.6739</v>
       </c>
       <c r="R17" t="n">
-        <v>10.7437</v>
+        <v>12.1114</v>
       </c>
       <c r="S17" t="n">
-        <v>-5.5386</v>
+        <v>0.4669</v>
       </c>
       <c r="T17" t="n">
-        <v>-2.9954</v>
+        <v>0.2037</v>
       </c>
       <c r="U17" t="n">
-        <v>-2.5435</v>
+        <v>0.2630999999999999</v>
       </c>
       <c r="V17" t="n">
-        <v>-1.4412</v>
+        <v>-8.984400000000001</v>
       </c>
       <c r="W17" t="n">
-        <v>4.764699999999999</v>
+        <v>0.3898</v>
       </c>
       <c r="X17" t="n">
-        <v>-6.2058</v>
+        <v>-9.3741</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>21</v>
       </c>
       <c r="D18" t="n">
-        <v>-30.0684</v>
+        <v>-24.5556</v>
       </c>
       <c r="E18" t="n">
-        <v>-15.1657</v>
+        <v>-12.6179</v>
       </c>
       <c r="F18" t="n">
-        <v>-14.9024</v>
+        <v>-11.9376</v>
       </c>
       <c r="G18" t="n">
         <v>-15.9089</v>
@@ -1858,13 +1858,13 @@
         <v>9.376200000000001</v>
       </c>
       <c r="S18" t="n">
-        <v>-6.4448</v>
+        <v>-0.9327000000000001</v>
       </c>
       <c r="T18" t="n">
-        <v>-4.481</v>
+        <v>-1.9332</v>
       </c>
       <c r="U18" t="n">
-        <v>-1.9639</v>
+        <v>1.0009</v>
       </c>
       <c r="V18" t="n">
         <v>-5.761</v>
@@ -1891,13 +1891,13 @@
         <v>26</v>
       </c>
       <c r="D19" t="n">
-        <v>-39.3198</v>
+        <v>-30.9619</v>
       </c>
       <c r="E19" t="n">
-        <v>-22.4906</v>
+        <v>-17.8004</v>
       </c>
       <c r="F19" t="n">
-        <v>-16.8288</v>
+        <v>-13.1617</v>
       </c>
       <c r="G19" t="n">
         <v>-0.8007000000000006</v>
@@ -1936,13 +1936,13 @@
         <v>29.6921</v>
       </c>
       <c r="S19" t="n">
-        <v>-14.37</v>
+        <v>-6.0127</v>
       </c>
       <c r="T19" t="n">
-        <v>-12.2963</v>
+        <v>-7.6056</v>
       </c>
       <c r="U19" t="n">
-        <v>-2.0742</v>
+        <v>1.5932</v>
       </c>
       <c r="V19" t="n">
         <v>-6.9582</v>
@@ -1969,13 +1969,13 @@
         <v>19</v>
       </c>
       <c r="D20" t="n">
-        <v>-45.3174</v>
+        <v>-45.2746</v>
       </c>
       <c r="E20" t="n">
-        <v>-35.5739</v>
+        <v>-37.3954</v>
       </c>
       <c r="F20" t="n">
-        <v>-9.743499999999999</v>
+        <v>-7.8791</v>
       </c>
       <c r="G20" t="n">
         <v>-12.3639</v>
@@ -2014,13 +2014,13 @@
         <v>26.176</v>
       </c>
       <c r="S20" t="n">
-        <v>0.9996</v>
+        <v>1.0426</v>
       </c>
       <c r="T20" t="n">
-        <v>-1.3542</v>
+        <v>-3.1755</v>
       </c>
       <c r="U20" t="n">
-        <v>2.3538</v>
+        <v>4.2181</v>
       </c>
       <c r="V20" t="n">
         <v>0.03659999999999997</v>
@@ -2047,19 +2047,19 @@
         <v>26</v>
       </c>
       <c r="D21" t="n">
-        <v>-129.2577</v>
+        <v>-108.1402</v>
       </c>
       <c r="E21" t="n">
-        <v>-36.7561</v>
+        <v>-29.7953</v>
       </c>
       <c r="F21" t="n">
-        <v>-92.49939999999999</v>
+        <v>-78.34419999999999</v>
       </c>
       <c r="G21" t="n">
         <v>-30.10199999999999</v>
       </c>
       <c r="H21" t="n">
-        <v>32.668</v>
+        <v>32.66799999999999</v>
       </c>
       <c r="I21" t="n">
         <v>-62.77070000000001</v>
@@ -2071,10 +2071,10 @@
         <v>231.2048</v>
       </c>
       <c r="L21" t="n">
-        <v>81.73150000000001</v>
+        <v>81.7315</v>
       </c>
       <c r="M21" t="n">
-        <v>-343.0372</v>
+        <v>-343.0371999999999</v>
       </c>
       <c r="N21" t="n">
         <v>-198.537</v>
@@ -2089,16 +2089,16 @@
         <v>-421.9392999999999</v>
       </c>
       <c r="R21" t="n">
-        <v>327.1992999999999</v>
+        <v>327.1993</v>
       </c>
       <c r="S21" t="n">
-        <v>-17.33649999999999</v>
+        <v>3.7799</v>
       </c>
       <c r="T21" t="n">
-        <v>-57.5985</v>
+        <v>-50.6372</v>
       </c>
       <c r="U21" t="n">
-        <v>40.2616</v>
+        <v>54.4182</v>
       </c>
       <c r="V21" t="n">
         <v>12.9228</v>

--- a/informes_data/Tercera FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_C.B. CUARTE DE HUERVA.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_C.B. CUARTE DE HUERVA.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X21"/>
+  <dimension ref="A1:X23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>G. RODRIGUEZ SOLER</t>
+          <t>R. DÍAZ DEL VALLE</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -562,76 +562,76 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D2" t="n">
-        <v>22.0203</v>
+        <v>23.8051</v>
       </c>
       <c r="E2" t="n">
-        <v>18.8879</v>
+        <v>23.8051</v>
       </c>
       <c r="F2" t="n">
-        <v>3.1325</v>
+        <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>17.6194</v>
+        <v>23.8051</v>
       </c>
       <c r="H2" t="n">
-        <v>-1.3963</v>
+        <v>11.6655</v>
       </c>
       <c r="I2" t="n">
-        <v>19.0157</v>
+        <v>12.1398</v>
       </c>
       <c r="J2" t="n">
-        <v>22.7969</v>
+        <v>23.8051</v>
       </c>
       <c r="K2" t="n">
-        <v>4.5854</v>
+        <v>11.6655</v>
       </c>
       <c r="L2" t="n">
-        <v>18.2115</v>
+        <v>12.1398</v>
       </c>
       <c r="M2" t="n">
-        <v>-5.1775</v>
+        <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>-5.9817</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>0.8042</v>
+        <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>-3.5163</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>-11.9159</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>8.399800000000001</v>
+        <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>-1.2135</v>
+        <v>0</v>
       </c>
       <c r="T2" t="n">
-        <v>-1.8001</v>
+        <v>0</v>
       </c>
       <c r="U2" t="n">
-        <v>0.5865999999999999</v>
+        <v>0</v>
       </c>
       <c r="V2" t="n">
-        <v>9.1305</v>
+        <v>0</v>
       </c>
       <c r="W2" t="n">
-        <v>9.806799999999999</v>
+        <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.6762999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>S. MENENDEZ PEREZ</t>
+          <t>G. RODRIGUEZ SOLER</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -640,76 +640,76 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>26</v>
+        <v>4</v>
       </c>
       <c r="D3" t="n">
-        <v>18.4149</v>
+        <v>22.0203</v>
       </c>
       <c r="E3" t="n">
-        <v>24.7425</v>
+        <v>18.8879</v>
       </c>
       <c r="F3" t="n">
-        <v>-6.327299999999998</v>
+        <v>3.1325</v>
       </c>
       <c r="G3" t="n">
-        <v>6.1248</v>
+        <v>17.6194</v>
       </c>
       <c r="H3" t="n">
-        <v>5.5973</v>
+        <v>-1.3963</v>
       </c>
       <c r="I3" t="n">
-        <v>0.527399999999999</v>
+        <v>19.0157</v>
       </c>
       <c r="J3" t="n">
-        <v>53.4568</v>
+        <v>22.7969</v>
       </c>
       <c r="K3" t="n">
-        <v>32.539</v>
+        <v>4.5854</v>
       </c>
       <c r="L3" t="n">
-        <v>20.9181</v>
+        <v>18.2115</v>
       </c>
       <c r="M3" t="n">
-        <v>-47.3318</v>
+        <v>-5.1775</v>
       </c>
       <c r="N3" t="n">
-        <v>-26.9419</v>
+        <v>-5.9817</v>
       </c>
       <c r="O3" t="n">
-        <v>-20.3902</v>
+        <v>0.8042</v>
       </c>
       <c r="P3" t="n">
-        <v>10.7438</v>
+        <v>-3.5163</v>
       </c>
       <c r="Q3" t="n">
-        <v>-33.9894</v>
+        <v>-11.9159</v>
       </c>
       <c r="R3" t="n">
-        <v>44.7336</v>
+        <v>8.399800000000001</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.9876</v>
+        <v>-1.2135</v>
       </c>
       <c r="T3" t="n">
-        <v>-8.799799999999999</v>
+        <v>-1.8001</v>
       </c>
       <c r="U3" t="n">
-        <v>6.8123</v>
+        <v>0.5865999999999999</v>
       </c>
       <c r="V3" t="n">
-        <v>3.5338</v>
+        <v>9.1305</v>
       </c>
       <c r="W3" t="n">
-        <v>14.0748</v>
+        <v>9.806799999999999</v>
       </c>
       <c r="X3" t="n">
-        <v>-10.5409</v>
+        <v>-0.6762999999999999</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>P. GIMENO MARTIN</t>
+          <t>S. MENENDEZ PEREZ</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -718,76 +718,76 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D4" t="n">
-        <v>15.9676</v>
+        <v>18.4149</v>
       </c>
       <c r="E4" t="n">
-        <v>28.1123</v>
+        <v>24.7425</v>
       </c>
       <c r="F4" t="n">
-        <v>-12.1444</v>
+        <v>-6.327299999999998</v>
       </c>
       <c r="G4" t="n">
-        <v>15.4114</v>
+        <v>6.1248</v>
       </c>
       <c r="H4" t="n">
-        <v>30.8557</v>
+        <v>5.5973</v>
       </c>
       <c r="I4" t="n">
-        <v>-15.4445</v>
+        <v>0.527399999999999</v>
       </c>
       <c r="J4" t="n">
-        <v>62.7335</v>
+        <v>53.4568</v>
       </c>
       <c r="K4" t="n">
-        <v>56.4375</v>
+        <v>32.539</v>
       </c>
       <c r="L4" t="n">
-        <v>6.2959</v>
+        <v>20.9181</v>
       </c>
       <c r="M4" t="n">
-        <v>-47.322</v>
+        <v>-47.3318</v>
       </c>
       <c r="N4" t="n">
-        <v>-25.582</v>
+        <v>-26.9419</v>
       </c>
       <c r="O4" t="n">
-        <v>-21.7399</v>
+        <v>-20.3902</v>
       </c>
       <c r="P4" t="n">
-        <v>-7.0323</v>
+        <v>10.7438</v>
       </c>
       <c r="Q4" t="n">
-        <v>-53.3284</v>
+        <v>-33.9894</v>
       </c>
       <c r="R4" t="n">
-        <v>46.2963</v>
+        <v>44.7336</v>
       </c>
       <c r="S4" t="n">
-        <v>-3.8264</v>
+        <v>-1.9876</v>
       </c>
       <c r="T4" t="n">
-        <v>-9.664899999999999</v>
+        <v>-8.799799999999999</v>
       </c>
       <c r="U4" t="n">
-        <v>5.8384</v>
+        <v>6.8123</v>
       </c>
       <c r="V4" t="n">
-        <v>11.4153</v>
+        <v>3.5338</v>
       </c>
       <c r="W4" t="n">
-        <v>28.3726</v>
+        <v>14.0748</v>
       </c>
       <c r="X4" t="n">
-        <v>-16.9569</v>
+        <v>-10.5409</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A. YOUNG MEDIERO</t>
+          <t>P. GIMENO MARTIN</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -796,76 +796,76 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="D5" t="n">
-        <v>9.584500000000002</v>
+        <v>15.9676</v>
       </c>
       <c r="E5" t="n">
-        <v>6.176600000000001</v>
+        <v>28.1123</v>
       </c>
       <c r="F5" t="n">
-        <v>3.4078</v>
+        <v>-12.1444</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.9678999999999993</v>
+        <v>15.4114</v>
       </c>
       <c r="H5" t="n">
-        <v>7.2208</v>
+        <v>30.8557</v>
       </c>
       <c r="I5" t="n">
-        <v>-8.188600000000001</v>
+        <v>-15.4445</v>
       </c>
       <c r="J5" t="n">
-        <v>11.579</v>
+        <v>62.7335</v>
       </c>
       <c r="K5" t="n">
-        <v>13.1505</v>
+        <v>56.4375</v>
       </c>
       <c r="L5" t="n">
-        <v>-1.5713</v>
+        <v>6.2959</v>
       </c>
       <c r="M5" t="n">
-        <v>-12.5469</v>
+        <v>-47.322</v>
       </c>
       <c r="N5" t="n">
-        <v>-5.929600000000001</v>
+        <v>-25.582</v>
       </c>
       <c r="O5" t="n">
-        <v>-6.6173</v>
+        <v>-21.7399</v>
       </c>
       <c r="P5" t="n">
-        <v>5.8604</v>
+        <v>-7.0323</v>
       </c>
       <c r="Q5" t="n">
-        <v>-10.7438</v>
+        <v>-53.3284</v>
       </c>
       <c r="R5" t="n">
-        <v>16.6043</v>
+        <v>46.2963</v>
       </c>
       <c r="S5" t="n">
-        <v>5.557399999999999</v>
+        <v>-3.8264</v>
       </c>
       <c r="T5" t="n">
-        <v>0.07709999999999999</v>
+        <v>-9.664899999999999</v>
       </c>
       <c r="U5" t="n">
-        <v>5.4801</v>
+        <v>5.8384</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.8651</v>
+        <v>11.4153</v>
       </c>
       <c r="W5" t="n">
-        <v>5.2643</v>
+        <v>28.3726</v>
       </c>
       <c r="X5" t="n">
-        <v>-6.1297</v>
+        <v>-16.9569</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>F. ALEN GARCIA</t>
+          <t>A. YOUNG MEDIERO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -874,76 +874,76 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D6" t="n">
-        <v>2.4485</v>
+        <v>9.584500000000002</v>
       </c>
       <c r="E6" t="n">
-        <v>1.7746</v>
+        <v>6.176600000000001</v>
       </c>
       <c r="F6" t="n">
-        <v>0.6739999999999999</v>
+        <v>3.4078</v>
       </c>
       <c r="G6" t="n">
-        <v>0.9076000000000002</v>
+        <v>-0.9678999999999993</v>
       </c>
       <c r="H6" t="n">
-        <v>0.4768000000000002</v>
+        <v>7.2208</v>
       </c>
       <c r="I6" t="n">
-        <v>0.4307</v>
+        <v>-8.188600000000001</v>
       </c>
       <c r="J6" t="n">
-        <v>1.0674</v>
+        <v>11.579</v>
       </c>
       <c r="K6" t="n">
-        <v>0.9055</v>
+        <v>13.1505</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1619</v>
+        <v>-1.5713</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.1599</v>
+        <v>-12.5469</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.4288</v>
+        <v>-5.929600000000001</v>
       </c>
       <c r="O6" t="n">
-        <v>0.2688</v>
+        <v>-6.6173</v>
       </c>
       <c r="P6" t="n">
-        <v>0.9766999999999999</v>
+        <v>5.8604</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.1953</v>
+        <v>-10.7438</v>
       </c>
       <c r="R6" t="n">
-        <v>1.172</v>
+        <v>16.6043</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.432</v>
+        <v>5.557399999999999</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.2613</v>
+        <v>0.07709999999999999</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.1707</v>
+        <v>5.4801</v>
       </c>
       <c r="V6" t="n">
-        <v>0.9963</v>
+        <v>-0.8651</v>
       </c>
       <c r="W6" t="n">
-        <v>1.1637</v>
+        <v>5.2643</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.1676</v>
+        <v>-6.1297</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>M. PORTALEZ MUR</t>
+          <t>M. PACÍFICO CANTARELLI</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -952,76 +952,76 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="D7" t="n">
-        <v>0.5248999999999997</v>
+        <v>2.449</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.4347</v>
+        <v>2.449</v>
       </c>
       <c r="F7" t="n">
-        <v>1.9598</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>7.055400000000001</v>
+        <v>2.449</v>
       </c>
       <c r="H7" t="n">
-        <v>31.5738</v>
+        <v>1.842</v>
       </c>
       <c r="I7" t="n">
-        <v>-24.5184</v>
+        <v>0.607</v>
       </c>
       <c r="J7" t="n">
-        <v>46.2183</v>
+        <v>2.449</v>
       </c>
       <c r="K7" t="n">
-        <v>52.2358</v>
+        <v>1.842</v>
       </c>
       <c r="L7" t="n">
-        <v>-6.0177</v>
+        <v>0.607</v>
       </c>
       <c r="M7" t="n">
-        <v>-39.1625</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>-20.662</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>-18.5006</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>-18.7529</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>-57.4306</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>38.6779</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>7.421</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>-5.6834</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>13.1045</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>4.8013</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>15.4613</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-10.6598</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Y. BOULHROUZI MADANI</t>
+          <t>F. ALEN GARCIA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1030,76 +1030,76 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>2.4485</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.0605</v>
+        <v>1.7746</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0605</v>
+        <v>0.6739999999999999</v>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>0.9076000000000002</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>0.4768000000000002</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>0.4307</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>1.0674</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>0.9055</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>0.1619</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>-0.1599</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>-0.4288</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>0.2688</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>0.9766999999999999</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-0.1953</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.172</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>-0.432</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.0605</v>
+        <v>-0.2613</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0605</v>
+        <v>-0.1707</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>0.9963</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.1637</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-0.1676</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>I. GIL PEREZ</t>
+          <t>M. PORTALEZ MUR</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1108,76 +1108,76 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.4047</v>
+        <v>0.5248999999999997</v>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
+        <v>-1.4347</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.4047</v>
+        <v>1.9598</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.4047</v>
+        <v>7.055400000000001</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>31.5738</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.4047</v>
+        <v>-24.5184</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>46.2183</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>52.2358</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>-6.0177</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.4047</v>
+        <v>-39.1625</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>-20.662</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.4047</v>
+        <v>-18.5006</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>-18.7529</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-57.4306</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>38.6779</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>7.421</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>-5.6834</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>13.1045</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>4.8013</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>15.4613</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-10.6598</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>D. MELINTE</t>
+          <t>Y. BOULHROUZI MADANI</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,22 +1189,22 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.4047</v>
+        <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
+        <v>-0.0605</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.4047</v>
+        <v>0.0605</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.4047</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.4047</v>
+        <v>0</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1216,13 +1216,13 @@
         <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.4047</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.4047</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
         <v>0</v>
@@ -1237,10 +1237,10 @@
         <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>-0.0605</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>0.0605</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>G. SOLA BEDMAR</t>
+          <t>D. MELINTE</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,58 +1267,58 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.356</v>
+        <v>-0.4047</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.8128</v>
+        <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.5432</v>
+        <v>-0.4047</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.7851</v>
+        <v>-0.4047</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.7721</v>
+        <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.013</v>
+        <v>-0.4047</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.9517</v>
+        <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.9389</v>
+        <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.0128</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.8334</v>
+        <v>-0.4047</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.8332000000000001</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.0002</v>
+        <v>-0.4047</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.586</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.1721</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>0.586</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>0.0151</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>0.311</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.2958</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1333,7 +1333,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>R. DÍAZ DEL VALLE</t>
+          <t>I. GIL PEREZ</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1342,76 +1342,76 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-5.758699999999999</v>
+        <v>-0.4047</v>
       </c>
       <c r="E12" t="n">
-        <v>-7.779900000000001</v>
+        <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>2.021199999999999</v>
+        <v>-0.4047</v>
       </c>
       <c r="G12" t="n">
-        <v>7.019</v>
+        <v>-0.4047</v>
       </c>
       <c r="H12" t="n">
-        <v>5.2521</v>
+        <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>1.767</v>
+        <v>-0.4047</v>
       </c>
       <c r="J12" t="n">
-        <v>17.5333</v>
+        <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>11.0371</v>
+        <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>6.4963</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>-10.5142</v>
+        <v>-0.4047</v>
       </c>
       <c r="N12" t="n">
-        <v>-5.7848</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>-4.7293</v>
+        <v>-0.4047</v>
       </c>
       <c r="P12" t="n">
-        <v>-13.8693</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>-27.3479</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>13.4788</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>3.06</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.7369</v>
+        <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>4.7969</v>
+        <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>-1.9683</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>3.7715</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-5.7398</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>M. KOTSEV</t>
+          <t>G. SOLA BEDMAR</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1420,76 +1420,76 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-9.2121</v>
+        <v>-2.356</v>
       </c>
       <c r="E13" t="n">
-        <v>-3.431100000000001</v>
+        <v>-1.8128</v>
       </c>
       <c r="F13" t="n">
-        <v>-5.781199999999999</v>
+        <v>-0.5432</v>
       </c>
       <c r="G13" t="n">
-        <v>-4.1777</v>
+        <v>-1.7851</v>
       </c>
       <c r="H13" t="n">
-        <v>-7.815399999999999</v>
+        <v>-1.7721</v>
       </c>
       <c r="I13" t="n">
-        <v>3.6375</v>
+        <v>-0.013</v>
       </c>
       <c r="J13" t="n">
-        <v>14.1097</v>
+        <v>-0.9517</v>
       </c>
       <c r="K13" t="n">
-        <v>3.856200000000001</v>
+        <v>-0.9389</v>
       </c>
       <c r="L13" t="n">
-        <v>10.2538</v>
+        <v>-0.0128</v>
       </c>
       <c r="M13" t="n">
-        <v>-18.2873</v>
+        <v>-0.8334</v>
       </c>
       <c r="N13" t="n">
-        <v>-11.6715</v>
+        <v>-0.8332000000000001</v>
       </c>
       <c r="O13" t="n">
-        <v>-6.616</v>
+        <v>-0.0002</v>
       </c>
       <c r="P13" t="n">
-        <v>-6.4464</v>
+        <v>-0.586</v>
       </c>
       <c r="Q13" t="n">
-        <v>-23.0504</v>
+        <v>-1.1721</v>
       </c>
       <c r="R13" t="n">
-        <v>16.6041</v>
+        <v>0.586</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.0467</v>
+        <v>0.0151</v>
       </c>
       <c r="T13" t="n">
-        <v>-1.3056</v>
+        <v>0.311</v>
       </c>
       <c r="U13" t="n">
-        <v>0.2587999999999999</v>
+        <v>-0.2958</v>
       </c>
       <c r="V13" t="n">
-        <v>2.458699999999999</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>6.8151</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>-4.3565</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>T. SEKOU MOUSSA</t>
+          <t>M. KOTSEV</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1498,76 +1498,76 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="D14" t="n">
-        <v>-11.5177</v>
+        <v>-9.2121</v>
       </c>
       <c r="E14" t="n">
-        <v>-9.774699999999999</v>
+        <v>-3.431100000000001</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.7429</v>
+        <v>-5.781199999999999</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.8016000000000003</v>
+        <v>-4.1777</v>
       </c>
       <c r="H14" t="n">
-        <v>-1.5276</v>
+        <v>-7.815399999999999</v>
       </c>
       <c r="I14" t="n">
-        <v>0.7261000000000001</v>
+        <v>3.6375</v>
       </c>
       <c r="J14" t="n">
-        <v>0.6217</v>
+        <v>14.1097</v>
       </c>
       <c r="K14" t="n">
-        <v>0.2980000000000002</v>
+        <v>3.856200000000001</v>
       </c>
       <c r="L14" t="n">
-        <v>0.3237</v>
+        <v>10.2538</v>
       </c>
       <c r="M14" t="n">
-        <v>-1.4233</v>
+        <v>-18.2873</v>
       </c>
       <c r="N14" t="n">
-        <v>-1.8255</v>
+        <v>-11.6715</v>
       </c>
       <c r="O14" t="n">
-        <v>0.4022</v>
+        <v>-6.616</v>
       </c>
       <c r="P14" t="n">
-        <v>-6.6417</v>
+        <v>-6.4464</v>
       </c>
       <c r="Q14" t="n">
-        <v>-9.9625</v>
+        <v>-23.0504</v>
       </c>
       <c r="R14" t="n">
-        <v>3.3208</v>
+        <v>16.6041</v>
       </c>
       <c r="S14" t="n">
-        <v>0.5349999999999999</v>
+        <v>-1.0467</v>
       </c>
       <c r="T14" t="n">
-        <v>0.8945</v>
+        <v>-1.3056</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.3596</v>
+        <v>0.2587999999999999</v>
       </c>
       <c r="V14" t="n">
-        <v>-4.609500000000001</v>
+        <v>2.458699999999999</v>
       </c>
       <c r="W14" t="n">
-        <v>-1.3284</v>
+        <v>6.8151</v>
       </c>
       <c r="X14" t="n">
-        <v>-3.2811</v>
+        <v>-4.3565</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>J. FERNANDEZ MANZANARES</t>
+          <t>T. SEKOU MOUSSA</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1576,76 +1576,76 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>26</v>
+        <v>4</v>
       </c>
       <c r="D15" t="n">
-        <v>-13.5641</v>
+        <v>-11.5177</v>
       </c>
       <c r="E15" t="n">
-        <v>1.405199999999999</v>
+        <v>-9.774699999999999</v>
       </c>
       <c r="F15" t="n">
-        <v>-14.9691</v>
+        <v>-1.7429</v>
       </c>
       <c r="G15" t="n">
-        <v>-30.3707</v>
+        <v>-0.8016000000000003</v>
       </c>
       <c r="H15" t="n">
-        <v>-12.3136</v>
+        <v>-1.5276</v>
       </c>
       <c r="I15" t="n">
-        <v>-18.057</v>
+        <v>0.7261000000000001</v>
       </c>
       <c r="J15" t="n">
-        <v>26.7924</v>
+        <v>0.6217</v>
       </c>
       <c r="K15" t="n">
-        <v>23.106</v>
+        <v>0.2980000000000002</v>
       </c>
       <c r="L15" t="n">
-        <v>3.686399999999999</v>
+        <v>0.3237</v>
       </c>
       <c r="M15" t="n">
-        <v>-57.1636</v>
+        <v>-1.4233</v>
       </c>
       <c r="N15" t="n">
-        <v>-35.4199</v>
+        <v>-1.8255</v>
       </c>
       <c r="O15" t="n">
-        <v>-21.7437</v>
+        <v>0.4022</v>
       </c>
       <c r="P15" t="n">
-        <v>2.7349</v>
+        <v>-6.6417</v>
       </c>
       <c r="Q15" t="n">
-        <v>-46.4916</v>
+        <v>-9.9625</v>
       </c>
       <c r="R15" t="n">
-        <v>49.2263</v>
+        <v>3.3208</v>
       </c>
       <c r="S15" t="n">
-        <v>2.9336</v>
+        <v>0.5349999999999999</v>
       </c>
       <c r="T15" t="n">
-        <v>-7.7679</v>
+        <v>0.8945</v>
       </c>
       <c r="U15" t="n">
-        <v>10.702</v>
+        <v>-0.3596</v>
       </c>
       <c r="V15" t="n">
-        <v>11.138</v>
+        <v>-4.609500000000001</v>
       </c>
       <c r="W15" t="n">
-        <v>28.8719</v>
+        <v>-1.3284</v>
       </c>
       <c r="X15" t="n">
-        <v>-17.7338</v>
+        <v>-3.2811</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>M. PACÍFICO CANTARELLI</t>
+          <t>J. FERNANDEZ MANZANARES</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1654,70 +1654,70 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="D16" t="n">
-        <v>-16.1221</v>
+        <v>-13.5641</v>
       </c>
       <c r="E16" t="n">
-        <v>-7.8285</v>
+        <v>1.405199999999999</v>
       </c>
       <c r="F16" t="n">
-        <v>-8.293900000000001</v>
+        <v>-14.9691</v>
       </c>
       <c r="G16" t="n">
-        <v>-9.3651</v>
+        <v>-30.3707</v>
       </c>
       <c r="H16" t="n">
-        <v>-6.261699999999999</v>
+        <v>-12.3136</v>
       </c>
       <c r="I16" t="n">
-        <v>-3.1037</v>
+        <v>-18.057</v>
       </c>
       <c r="J16" t="n">
-        <v>3.9957</v>
+        <v>26.7924</v>
       </c>
       <c r="K16" t="n">
-        <v>0.7531999999999998</v>
+        <v>23.106</v>
       </c>
       <c r="L16" t="n">
-        <v>3.242099999999999</v>
+        <v>3.686399999999999</v>
       </c>
       <c r="M16" t="n">
-        <v>-13.3605</v>
+        <v>-57.1636</v>
       </c>
       <c r="N16" t="n">
-        <v>-7.014799999999999</v>
+        <v>-35.4199</v>
       </c>
       <c r="O16" t="n">
-        <v>-6.3458</v>
+        <v>-21.7437</v>
       </c>
       <c r="P16" t="n">
-        <v>-3.5161</v>
+        <v>2.7349</v>
       </c>
       <c r="Q16" t="n">
-        <v>-14.2599</v>
+        <v>-46.4916</v>
       </c>
       <c r="R16" t="n">
-        <v>10.7437</v>
+        <v>49.2263</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.8001</v>
+        <v>2.9336</v>
       </c>
       <c r="T16" t="n">
-        <v>-2.3288</v>
+        <v>-7.7679</v>
       </c>
       <c r="U16" t="n">
-        <v>0.5289</v>
+        <v>10.702</v>
       </c>
       <c r="V16" t="n">
-        <v>-1.4412</v>
+        <v>11.138</v>
       </c>
       <c r="W16" t="n">
-        <v>4.764699999999999</v>
+        <v>28.8719</v>
       </c>
       <c r="X16" t="n">
-        <v>-6.2058</v>
+        <v>-17.7338</v>
       </c>
     </row>
     <row r="17">
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>O. LOPEZ SANCHEZ</t>
+          <t>M. PACIFICO CANTARELLI</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1810,76 +1810,76 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="D18" t="n">
-        <v>-24.5556</v>
+        <v>-18.5711</v>
       </c>
       <c r="E18" t="n">
-        <v>-12.6179</v>
+        <v>-10.2775</v>
       </c>
       <c r="F18" t="n">
-        <v>-11.9376</v>
+        <v>-8.293900000000001</v>
       </c>
       <c r="G18" t="n">
-        <v>-15.9089</v>
+        <v>-11.8138</v>
       </c>
       <c r="H18" t="n">
-        <v>-6.6678</v>
+        <v>-8.1035</v>
       </c>
       <c r="I18" t="n">
-        <v>-9.2407</v>
+        <v>-3.7107</v>
       </c>
       <c r="J18" t="n">
-        <v>1.0322</v>
+        <v>1.5468</v>
       </c>
       <c r="K18" t="n">
-        <v>1.9047</v>
+        <v>-1.0887</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.8722000000000002</v>
+        <v>2.6351</v>
       </c>
       <c r="M18" t="n">
-        <v>-16.9411</v>
+        <v>-13.3605</v>
       </c>
       <c r="N18" t="n">
-        <v>-8.5724</v>
+        <v>-7.014799999999999</v>
       </c>
       <c r="O18" t="n">
-        <v>-8.3683</v>
+        <v>-6.3458</v>
       </c>
       <c r="P18" t="n">
-        <v>-1.9537</v>
+        <v>-3.5161</v>
       </c>
       <c r="Q18" t="n">
-        <v>-11.3297</v>
+        <v>-14.2599</v>
       </c>
       <c r="R18" t="n">
-        <v>9.376200000000001</v>
+        <v>10.7437</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.9327000000000001</v>
+        <v>-1.8001</v>
       </c>
       <c r="T18" t="n">
-        <v>-1.9332</v>
+        <v>-2.3288</v>
       </c>
       <c r="U18" t="n">
-        <v>1.0009</v>
+        <v>0.5289</v>
       </c>
       <c r="V18" t="n">
-        <v>-5.761</v>
+        <v>-1.4412</v>
       </c>
       <c r="W18" t="n">
-        <v>-0.387</v>
+        <v>4.764699999999999</v>
       </c>
       <c r="X18" t="n">
-        <v>-5.374099999999999</v>
+        <v>-6.2058</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>D. CAJAL PENACHO</t>
+          <t>O. LOPEZ SANCHEZ</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1888,76 +1888,76 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="D19" t="n">
-        <v>-30.9619</v>
+        <v>-24.5556</v>
       </c>
       <c r="E19" t="n">
-        <v>-17.8004</v>
+        <v>-12.6179</v>
       </c>
       <c r="F19" t="n">
-        <v>-13.1617</v>
+        <v>-11.9376</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.8007000000000006</v>
+        <v>-15.9089</v>
       </c>
       <c r="H19" t="n">
-        <v>-2.9547</v>
+        <v>-6.6678</v>
       </c>
       <c r="I19" t="n">
-        <v>2.1536</v>
+        <v>-9.2407</v>
       </c>
       <c r="J19" t="n">
-        <v>35.5789</v>
+        <v>1.0322</v>
       </c>
       <c r="K19" t="n">
-        <v>16.6832</v>
+        <v>1.9047</v>
       </c>
       <c r="L19" t="n">
-        <v>18.8955</v>
+        <v>-0.8722000000000002</v>
       </c>
       <c r="M19" t="n">
-        <v>-36.3796</v>
+        <v>-16.9411</v>
       </c>
       <c r="N19" t="n">
-        <v>-19.6379</v>
+        <v>-8.5724</v>
       </c>
       <c r="O19" t="n">
-        <v>-16.7421</v>
+        <v>-8.3683</v>
       </c>
       <c r="P19" t="n">
-        <v>-17.1901</v>
+        <v>-1.9537</v>
       </c>
       <c r="Q19" t="n">
-        <v>-46.8823</v>
+        <v>-11.3297</v>
       </c>
       <c r="R19" t="n">
-        <v>29.6921</v>
+        <v>9.376200000000001</v>
       </c>
       <c r="S19" t="n">
-        <v>-6.0127</v>
+        <v>-0.9327000000000001</v>
       </c>
       <c r="T19" t="n">
-        <v>-7.6056</v>
+        <v>-1.9332</v>
       </c>
       <c r="U19" t="n">
-        <v>1.5932</v>
+        <v>1.0009</v>
       </c>
       <c r="V19" t="n">
-        <v>-6.9582</v>
+        <v>-5.761</v>
       </c>
       <c r="W19" t="n">
-        <v>1.1088</v>
+        <v>-0.387</v>
       </c>
       <c r="X19" t="n">
-        <v>-8.067</v>
+        <v>-5.374099999999999</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>N. CLEDJO HOUNGUES</t>
+          <t>R. DIAZ DEL VALLE</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1966,76 +1966,76 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="D20" t="n">
-        <v>-45.2746</v>
+        <v>-29.5638</v>
       </c>
       <c r="E20" t="n">
-        <v>-37.3954</v>
+        <v>-31.5851</v>
       </c>
       <c r="F20" t="n">
-        <v>-7.8791</v>
+        <v>2.021199999999999</v>
       </c>
       <c r="G20" t="n">
-        <v>-12.3639</v>
+        <v>-16.7862</v>
       </c>
       <c r="H20" t="n">
-        <v>-2.212300000000001</v>
+        <v>-6.4133</v>
       </c>
       <c r="I20" t="n">
-        <v>-10.1517</v>
+        <v>-10.3729</v>
       </c>
       <c r="J20" t="n">
-        <v>14.2502</v>
+        <v>-6.2719</v>
       </c>
       <c r="K20" t="n">
-        <v>14.4062</v>
+        <v>-0.6283999999999996</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.1558999999999998</v>
+        <v>-5.6436</v>
       </c>
       <c r="M20" t="n">
-        <v>-26.614</v>
+        <v>-10.5142</v>
       </c>
       <c r="N20" t="n">
-        <v>-16.6185</v>
+        <v>-5.7848</v>
       </c>
       <c r="O20" t="n">
-        <v>-9.995699999999999</v>
+        <v>-4.7293</v>
       </c>
       <c r="P20" t="n">
-        <v>-33.9894</v>
+        <v>-13.8693</v>
       </c>
       <c r="Q20" t="n">
-        <v>-60.1656</v>
+        <v>-27.3479</v>
       </c>
       <c r="R20" t="n">
-        <v>26.176</v>
+        <v>13.4788</v>
       </c>
       <c r="S20" t="n">
-        <v>1.0426</v>
+        <v>3.06</v>
       </c>
       <c r="T20" t="n">
-        <v>-3.1755</v>
+        <v>-1.7369</v>
       </c>
       <c r="U20" t="n">
-        <v>4.2181</v>
+        <v>4.7969</v>
       </c>
       <c r="V20" t="n">
-        <v>0.03659999999999997</v>
+        <v>-1.9683</v>
       </c>
       <c r="W20" t="n">
-        <v>11.6956</v>
+        <v>3.7715</v>
       </c>
       <c r="X20" t="n">
-        <v>-11.6591</v>
+        <v>-5.7398</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>--- TOTAL ---</t>
+          <t>D. CAJAL PENACHO</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,66 +2047,222 @@
         <v>26</v>
       </c>
       <c r="D21" t="n">
+        <v>-30.9619</v>
+      </c>
+      <c r="E21" t="n">
+        <v>-17.8004</v>
+      </c>
+      <c r="F21" t="n">
+        <v>-13.1617</v>
+      </c>
+      <c r="G21" t="n">
+        <v>-0.8007000000000006</v>
+      </c>
+      <c r="H21" t="n">
+        <v>-2.9547</v>
+      </c>
+      <c r="I21" t="n">
+        <v>2.1536</v>
+      </c>
+      <c r="J21" t="n">
+        <v>35.5789</v>
+      </c>
+      <c r="K21" t="n">
+        <v>16.6832</v>
+      </c>
+      <c r="L21" t="n">
+        <v>18.8955</v>
+      </c>
+      <c r="M21" t="n">
+        <v>-36.3796</v>
+      </c>
+      <c r="N21" t="n">
+        <v>-19.6379</v>
+      </c>
+      <c r="O21" t="n">
+        <v>-16.7421</v>
+      </c>
+      <c r="P21" t="n">
+        <v>-17.1901</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>-46.8823</v>
+      </c>
+      <c r="R21" t="n">
+        <v>29.6921</v>
+      </c>
+      <c r="S21" t="n">
+        <v>-6.0127</v>
+      </c>
+      <c r="T21" t="n">
+        <v>-7.6056</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1.5932</v>
+      </c>
+      <c r="V21" t="n">
+        <v>-6.9582</v>
+      </c>
+      <c r="W21" t="n">
+        <v>1.1088</v>
+      </c>
+      <c r="X21" t="n">
+        <v>-8.067</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>N. CLEDJO HOUNGUES</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>C.B. CUARTE DE HUERVA</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>19</v>
+      </c>
+      <c r="D22" t="n">
+        <v>-45.2746</v>
+      </c>
+      <c r="E22" t="n">
+        <v>-37.3954</v>
+      </c>
+      <c r="F22" t="n">
+        <v>-7.8791</v>
+      </c>
+      <c r="G22" t="n">
+        <v>-12.3639</v>
+      </c>
+      <c r="H22" t="n">
+        <v>-2.212300000000001</v>
+      </c>
+      <c r="I22" t="n">
+        <v>-10.1517</v>
+      </c>
+      <c r="J22" t="n">
+        <v>14.2502</v>
+      </c>
+      <c r="K22" t="n">
+        <v>14.4062</v>
+      </c>
+      <c r="L22" t="n">
+        <v>-0.1558999999999998</v>
+      </c>
+      <c r="M22" t="n">
+        <v>-26.614</v>
+      </c>
+      <c r="N22" t="n">
+        <v>-16.6185</v>
+      </c>
+      <c r="O22" t="n">
+        <v>-9.995699999999999</v>
+      </c>
+      <c r="P22" t="n">
+        <v>-33.9894</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>-60.1656</v>
+      </c>
+      <c r="R22" t="n">
+        <v>26.176</v>
+      </c>
+      <c r="S22" t="n">
+        <v>1.0426</v>
+      </c>
+      <c r="T22" t="n">
+        <v>-3.1755</v>
+      </c>
+      <c r="U22" t="n">
+        <v>4.2181</v>
+      </c>
+      <c r="V22" t="n">
+        <v>0.03659999999999997</v>
+      </c>
+      <c r="W22" t="n">
+        <v>11.6956</v>
+      </c>
+      <c r="X22" t="n">
+        <v>-11.6591</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>--- TOTAL ---</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>C.B. CUARTE DE HUERVA</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>26</v>
+      </c>
+      <c r="D23" t="n">
         <v>-108.1402</v>
       </c>
-      <c r="E21" t="n">
-        <v>-29.7953</v>
-      </c>
-      <c r="F21" t="n">
-        <v>-78.34419999999999</v>
-      </c>
-      <c r="G21" t="n">
-        <v>-30.10199999999999</v>
-      </c>
-      <c r="H21" t="n">
-        <v>32.66799999999999</v>
-      </c>
-      <c r="I21" t="n">
-        <v>-62.77070000000001</v>
-      </c>
-      <c r="J21" t="n">
+      <c r="E23" t="n">
+        <v>-29.7954</v>
+      </c>
+      <c r="F23" t="n">
+        <v>-78.3442</v>
+      </c>
+      <c r="G23" t="n">
+        <v>-30.10179999999999</v>
+      </c>
+      <c r="H23" t="n">
+        <v>32.6683</v>
+      </c>
+      <c r="I23" t="n">
+        <v>-62.77080000000002</v>
+      </c>
+      <c r="J23" t="n">
         <v>312.936</v>
       </c>
-      <c r="K21" t="n">
-        <v>231.2048</v>
-      </c>
-      <c r="L21" t="n">
-        <v>81.7315</v>
-      </c>
-      <c r="M21" t="n">
-        <v>-343.0371999999999</v>
-      </c>
-      <c r="N21" t="n">
+      <c r="K23" t="n">
+        <v>231.2049</v>
+      </c>
+      <c r="L23" t="n">
+        <v>81.73139999999999</v>
+      </c>
+      <c r="M23" t="n">
+        <v>-343.0372</v>
+      </c>
+      <c r="N23" t="n">
         <v>-198.537</v>
       </c>
-      <c r="O21" t="n">
+      <c r="O23" t="n">
         <v>-144.501</v>
       </c>
-      <c r="P21" t="n">
+      <c r="P23" t="n">
         <v>-94.74099999999999</v>
       </c>
-      <c r="Q21" t="n">
+      <c r="Q23" t="n">
         <v>-421.9392999999999</v>
       </c>
-      <c r="R21" t="n">
-        <v>327.1993</v>
-      </c>
-      <c r="S21" t="n">
-        <v>3.7799</v>
-      </c>
-      <c r="T21" t="n">
+      <c r="R23" t="n">
+        <v>327.1992999999999</v>
+      </c>
+      <c r="S23" t="n">
+        <v>3.779899999999999</v>
+      </c>
+      <c r="T23" t="n">
         <v>-50.6372</v>
       </c>
-      <c r="U21" t="n">
-        <v>54.4182</v>
-      </c>
-      <c r="V21" t="n">
+      <c r="U23" t="n">
+        <v>54.41820000000001</v>
+      </c>
+      <c r="V23" t="n">
         <v>12.9228</v>
       </c>
-      <c r="W21" t="n">
+      <c r="W23" t="n">
         <v>129.8455</v>
       </c>
-      <c r="X21" t="n">
+      <c r="X23" t="n">
         <v>-116.9225</v>
       </c>
     </row>
